--- a/diseases/d144/2026-2029.xlsx
+++ b/diseases/d144/2026-2029.xlsx
@@ -12466,12 +12466,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -12496,22 +12496,22 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O83" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R83" t="n">
-        <v>0</v>
+        <v>0.001633616815131532</v>
       </c>
       <c r="S83" t="inlineStr">
         <is>
@@ -12544,42 +12544,42 @@
       </c>
       <c r="AV83" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA83" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB83" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC83" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -12611,12 +12611,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -12689,40 +12689,185 @@
       </c>
       <c r="AV84" t="inlineStr">
         <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA84" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB84" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC84" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>D144</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>creutzfeldt-jakob-disease</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Creutzfeldt-Jakob disease</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>D144</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Creutzfeldt-Jakob disease</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>克雅氏病</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Prion</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N85" t="n">
+        <v>0</v>
+      </c>
+      <c r="O85" t="n">
+        <v>0</v>
+      </c>
+      <c r="R85" t="n">
+        <v>0</v>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP85" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR85" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS85" t="inlineStr"/>
+      <c r="AT85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV85" t="inlineStr">
+        <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW84" t="inlineStr">
+      <c r="AW85" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX84" t="inlineStr">
+      <c r="AX85" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY84" t="inlineStr">
+      <c r="AY85" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ84" t="inlineStr">
+      <c r="AZ85" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA84" t="inlineStr">
+      <c r="BA85" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB84" t="inlineStr">
+      <c r="BB85" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC84" t="inlineStr">
+      <c r="BC85" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -12844,7 +12989,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10">
@@ -12854,7 +12999,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="11">
@@ -12906,7 +13051,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d144/2026-2029.xlsx
+++ b/diseases/d144/2026-2029.xlsx
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R85" t="n">
-        <v>0</v>
+        <v>0.001937969923792046</v>
       </c>
       <c r="S85" t="inlineStr">
         <is>
@@ -12870,6 +12870,151 @@
       <c r="BC85" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>D144</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>creutzfeldt-jakob-disease</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Creutzfeldt-Jakob disease</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>D144</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Creutzfeldt-Jakob disease</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>克雅氏病</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Prion</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N86" t="n">
+        <v>3</v>
+      </c>
+      <c r="O86" t="n">
+        <v>3</v>
+      </c>
+      <c r="R86" t="n">
+        <v>0.002450425222697299</v>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO86" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP86" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR86" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS86" t="inlineStr"/>
+      <c r="AT86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV86" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA86" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB86" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC86" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -12906,7 +13051,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -12989,7 +13134,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10">
@@ -12999,7 +13144,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11">
@@ -13051,7 +13196,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d144/2026-2029.xlsx
+++ b/diseases/d144/2026-2029.xlsx
@@ -9629,13 +9629,13 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R63" t="n">
-        <v>0.003875939847584092</v>
+        <v>0.005813909771376137</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="N85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R85" t="n">
-        <v>0.001937969923792046</v>
+        <v>0</v>
       </c>
       <c r="S85" t="inlineStr">
         <is>

--- a/diseases/d144/2026-2029.xlsx
+++ b/diseases/d144/2026-2029.xlsx
@@ -11780,13 +11780,13 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R78" t="n">
-        <v>0</v>
+        <v>0.001937969923792046</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
@@ -13196,7 +13196,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d144/2026-2029.xlsx
+++ b/diseases/d144/2026-2029.xlsx
@@ -8203,13 +8203,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>0.00367281181951979</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -10499,13 +10499,13 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>0.00367281181951979</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -11741,12 +11741,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -11780,13 +11780,13 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R78" t="n">
-        <v>0.001937969923792046</v>
+        <v>0</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
@@ -11819,42 +11819,42 @@
       </c>
       <c r="AV78" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB78" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC78" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -11886,12 +11886,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -11916,7 +11916,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -11925,13 +11925,13 @@
         </is>
       </c>
       <c r="N79" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O79" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R79" t="n">
-        <v>0.003267233630263065</v>
+        <v>0.001937969923792046</v>
       </c>
       <c r="S79" t="inlineStr">
         <is>
@@ -11964,42 +11964,42 @@
       </c>
       <c r="AV79" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB79" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC79" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -12061,7 +12061,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -12070,13 +12070,13 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O80" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R80" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0.003267233630263065</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
@@ -12206,7 +12206,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -12215,13 +12215,13 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O81" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R81" t="n">
-        <v>0.001633616815131532</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S81" t="inlineStr">
         <is>
@@ -12351,7 +12351,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -12360,13 +12360,13 @@
         </is>
       </c>
       <c r="N82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R82" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0.001633616815131532</v>
       </c>
       <c r="S82" t="inlineStr">
         <is>
@@ -12496,7 +12496,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -12505,13 +12505,13 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O83" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R83" t="n">
-        <v>0.001633616815131532</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S83" t="inlineStr">
         <is>
@@ -12611,12 +12611,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -12641,22 +12641,22 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O84" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R84" t="n">
-        <v>0</v>
+        <v>0.001633616815131532</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
@@ -12689,42 +12689,42 @@
       </c>
       <c r="AV84" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA84" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB84" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC84" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -12756,12 +12756,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -12834,42 +12834,42 @@
       </c>
       <c r="AV85" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA85" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB85" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC85" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -12901,12 +12901,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -12931,7 +12931,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -12940,13 +12940,13 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R86" t="n">
-        <v>0.002450425222697299</v>
+        <v>0</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
@@ -12979,40 +12979,330 @@
       </c>
       <c r="AV86" t="inlineStr">
         <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA86" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB86" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC86" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>D144</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>creutzfeldt-jakob-disease</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Creutzfeldt-Jakob disease</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>D144</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Creutzfeldt-Jakob disease</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>克雅氏病</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Prion</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N87" t="n">
+        <v>3</v>
+      </c>
+      <c r="O87" t="n">
+        <v>3</v>
+      </c>
+      <c r="R87" t="n">
+        <v>0.002450425222697299</v>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO87" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP87" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR87" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS87" t="inlineStr"/>
+      <c r="AT87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV87" t="inlineStr">
+        <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="AW86" t="inlineStr">
+      <c r="AW87" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="AX86" t="inlineStr">
+      <c r="AX87" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="AY86" t="inlineStr">
+      <c r="AY87" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ86" t="inlineStr">
+      <c r="AZ87" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="BA86" t="inlineStr">
+      <c r="BA87" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="BB86" t="inlineStr">
+      <c r="BB87" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="BC86" t="inlineStr">
+      <c r="BC87" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>D144</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>creutzfeldt-jakob-disease</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Creutzfeldt-Jakob disease</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>D144</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Creutzfeldt-Jakob disease</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>克雅氏病</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Prion</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N88" t="n">
+        <v>3</v>
+      </c>
+      <c r="O88" t="n">
+        <v>3</v>
+      </c>
+      <c r="R88" t="n">
+        <v>0.002450425222697299</v>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO88" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP88" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR88" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS88" t="inlineStr"/>
+      <c r="AT88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV88" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA88" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB88" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC88" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -13051,7 +13341,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -13134,7 +13424,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10">
@@ -13144,7 +13434,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="11">
@@ -13196,7 +13486,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>121</v>
+        <v>126</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d144/2026-2029.xlsx
+++ b/diseases/d144/2026-2029.xlsx
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R85" t="n">
-        <v>0</v>
+        <v>0.00367281181951979</v>
       </c>
       <c r="S85" t="inlineStr">
         <is>
@@ -13305,6 +13305,296 @@
       <c r="BC88" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>D144</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>creutzfeldt-jakob-disease</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Creutzfeldt-Jakob disease</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>D144</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Creutzfeldt-Jakob disease</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>克雅氏病</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Prion</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N89" t="n">
+        <v>2</v>
+      </c>
+      <c r="O89" t="n">
+        <v>2</v>
+      </c>
+      <c r="R89" t="n">
+        <v>0.001633616815131532</v>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO89" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP89" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR89" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS89" t="inlineStr"/>
+      <c r="AT89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV89" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA89" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB89" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC89" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>D144</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>creutzfeldt-jakob-disease</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Creutzfeldt-Jakob disease</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>D144</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Creutzfeldt-Jakob disease</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>克雅氏病</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Prion</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N90" t="n">
+        <v>0</v>
+      </c>
+      <c r="O90" t="n">
+        <v>0</v>
+      </c>
+      <c r="R90" t="n">
+        <v>0</v>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO90" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP90" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR90" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS90" t="inlineStr"/>
+      <c r="AT90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV90" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA90" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB90" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC90" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -13341,7 +13631,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -13424,7 +13714,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10">
@@ -13434,7 +13724,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="11">
@@ -13486,7 +13776,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d144/2026-2029.xlsx
+++ b/diseases/d144/2026-2029.xlsx
@@ -776,6 +776,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -921,6 +926,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1066,6 +1076,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1211,6 +1226,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1356,6 +1376,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1492,6 +1517,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1637,6 +1667,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1782,6 +1817,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1918,6 +1958,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2063,6 +2108,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2208,6 +2258,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2948,6 +3003,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3093,6 +3153,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3238,6 +3303,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3383,6 +3453,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3528,6 +3603,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3673,6 +3753,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3818,6 +3903,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3963,6 +4053,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4099,6 +4194,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4244,6 +4344,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4389,6 +4494,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5129,6 +5239,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5274,6 +5389,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5419,6 +5539,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5564,6 +5689,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5709,6 +5839,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5854,6 +5989,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5999,6 +6139,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6144,6 +6289,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6280,6 +6430,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6425,6 +6580,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6570,6 +6730,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7307,6 +7472,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7452,6 +7622,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7597,6 +7772,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7742,6 +7922,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7887,6 +8072,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8032,6 +8222,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8177,6 +8372,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8322,6 +8522,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8467,6 +8672,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8612,6 +8822,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8757,6 +8972,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9494,6 +9714,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9639,6 +9864,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO63" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9784,6 +10014,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO64" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9929,6 +10164,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO65" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10074,6 +10314,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO66" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10219,6 +10464,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10364,6 +10614,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO68" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10509,6 +10764,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO69" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10654,6 +10914,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO70" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10799,6 +11064,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO71" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10944,6 +11214,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO72" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11829,6 +12104,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO78" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11974,6 +12254,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO79" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12119,6 +12404,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO80" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12264,6 +12554,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO81" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12409,6 +12704,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO82" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12554,6 +12854,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO83" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12699,6 +13004,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO84" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12844,6 +13154,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO85" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12989,6 +13304,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO86" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13134,6 +13454,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO87" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13279,6 +13604,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO88" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14004,6 +14334,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO93" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14149,6 +14484,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO94" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14294,6 +14634,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO95" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14439,6 +14784,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO96" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14584,6 +14934,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO97" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14720,6 +15075,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO98" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14865,6 +15225,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO99" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15010,6 +15375,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO100" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15155,6 +15525,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO101" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15300,6 +15675,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO102" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15445,6 +15825,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO103" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16315,6 +16700,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO109" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16460,6 +16850,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO110" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16605,6 +17000,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO111" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16750,6 +17150,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO112" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16895,6 +17300,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO113" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17040,6 +17450,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO114" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17176,6 +17591,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO115" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17321,6 +17741,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO116" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17466,6 +17891,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO117" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17611,6 +18041,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO118" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17756,6 +18191,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO119" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18626,6 +19066,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO125" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18771,6 +19216,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO126" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18916,6 +19366,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO127" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19061,6 +19516,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO128" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19206,6 +19666,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO129" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19351,6 +19816,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO130" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19496,6 +19966,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO131" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19632,6 +20107,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO132" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19777,6 +20257,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO133" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19922,6 +20407,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO134" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20645,6 +21135,11 @@
       <c r="S139" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO139" t="inlineStr">

--- a/diseases/d144/2026-2029.xlsx
+++ b/diseases/d144/2026-2029.xlsx
@@ -20394,13 +20394,13 @@
         </is>
       </c>
       <c r="N134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R134" t="n">
-        <v>0</v>
+        <v>0.001937969923792046</v>
       </c>
       <c r="S134" t="inlineStr">
         <is>
@@ -21385,7 +21385,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d144/2026-2029.xlsx
+++ b/diseases/d144/2026-2029.xlsx
@@ -21207,6 +21207,151 @@
         </is>
       </c>
     </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>D144</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>creutzfeldt-jakob-disease</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Creutzfeldt-Jakob disease</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>D144</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>Creutzfeldt-Jakob disease</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>克雅氏病</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Prion</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N140" t="n">
+        <v>0</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0</v>
+      </c>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO140" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP140" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR140" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS140" t="inlineStr"/>
+      <c r="AT140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU140" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV140" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW140" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX140" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY140" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA140" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB140" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC140" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -21240,7 +21385,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -21323,7 +21468,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="10">
@@ -21333,7 +21478,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11">
